--- a/2.xlsx
+++ b/2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\we-compare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F45E6F-4346-418D-BE59-E9914570DCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A19DDC3-C07E-4A5F-8EC6-A957855D30A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>倒是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -370,6 +378,14 @@
       <c r="A8">
         <v>232</v>
       </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L9" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M11">
